--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0 Hansoll AI\Design Terminology Organization\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABAC964-CE60-4FBF-B8A5-DABBB0175146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBD6FA5-DF7F-4EC2-BC51-82DBB12DB75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="495" windowWidth="21600" windowHeight="14235" xr2:uid="{DCA174AC-C2FF-452A-B0BB-597EA014E074}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="14235" xr2:uid="{DCA174AC-C2FF-452A-B0BB-597EA014E074}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX LIST" sheetId="6" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="188">
   <si>
     <t>ALL</t>
   </si>
@@ -699,6 +699,10 @@
   </si>
   <si>
     <t>Use Out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Image</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1090,7 +1094,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F2E287-6D98-4339-B90C-73BCC1706FAF}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
@@ -1102,10 +1106,10 @@
     <col min="7" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="11.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.375" customWidth="1"/>
-    <col min="11" max="11" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="7.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1139,8 +1143,11 @@
       <c r="K1" s="13" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1152,8 +1159,9 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-    </row>
-    <row r="3" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1165,8 +1173,9 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1178,8 +1187,9 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1191,8 +1201,9 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1204,8 +1215,9 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1217,8 +1229,9 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1230,8 +1243,9 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1243,8 +1257,9 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1256,8 +1271,9 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1269,8 +1285,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1282,8 +1299,9 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1295,8 +1313,9 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1308,8 +1327,9 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1321,8 +1341,9 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1334,8 +1355,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1347,8 +1369,9 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1360,8 +1383,9 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1373,8 +1397,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1386,8 +1411,9 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1399,8 +1425,9 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1412,8 +1439,9 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1425,8 +1453,9 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -1438,8 +1467,9 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1451,8 +1481,9 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1464,8 +1495,9 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -1477,8 +1509,9 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1490,8 +1523,9 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -1503,8 +1537,9 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -1516,8 +1551,9 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1529,8 +1565,9 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="1:12" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -1542,6 +1579,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
